--- a/site/leagues/proliga/2026_2027/xlsx/team_packs/team_pack_SBC.xlsx
+++ b/site/leagues/proliga/2026_2027/xlsx/team_packs/team_pack_SBC.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$B$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'rotation'!$A$1:$U$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'rotation'!$A$1:$U$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'key_lineups'!$A$1:$L$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'duos_trios'!$A$1:$J$7</definedName>
   </definedNames>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>M. Terry (29 ppg)</t>
+          <t>M. Terry (27.3 ppg)</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>M. Tavares (37.8 mpg)</t>
+          <t>M. Tavares (36.8 mpg)</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>T. Espada (55.6%)</t>
+          <t>T. Espada (50.0%)</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A. Nongo | D. Hall | M. Tavares | M. Terry | T. Espada (9.5 net)</t>
+          <t>A. Nongo | D. Hall | M. Tavares | M. Terry | T. Espada (17.7 net)</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>M. Tavares | M. Terry (-0.6 net)</t>
+          <t>M. Tavares | M. Terry (-2.4 net)</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>D. Hall | M. Tavares | M. Terry (1.5 net)</t>
+          <t>D. Hall | M. Tavares | M. Terry (-1.4 net)</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U5"/>
+  <dimension ref="A1:U6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -718,19 +718,19 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>75.59999999999999</v>
+        <v>110.4</v>
       </c>
       <c r="G2" t="n">
-        <v>37.8</v>
+        <v>36.8</v>
       </c>
       <c r="H2" t="n">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="I2" t="n">
         <v>7</v>
@@ -739,22 +739,22 @@
         <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="L2" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -764,23 +764,23 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>61.7%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>0.5</v>
+        <v>-0.3</v>
       </c>
       <c r="T2" t="n">
-        <v>36.9</v>
+        <v>16.3</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>high-minutes, primary-scorer, efficient</t>
+          <t>high-minutes, impact</t>
         </is>
       </c>
     </row>
@@ -797,65 +797,65 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>71.2</v>
+        <v>107.4</v>
       </c>
       <c r="G3" t="n">
-        <v>35.6</v>
+        <v>35.8</v>
       </c>
       <c r="H3" t="n">
-        <v>29</v>
+        <v>27.3</v>
       </c>
       <c r="I3" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J3" t="n">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="K3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L3" t="n">
         <v>1</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.5</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>-1</v>
+        <v>-1.3</v>
       </c>
       <c r="T3" t="n">
-        <v>-11.9</v>
+        <v>-9</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -876,65 +876,65 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>63.8</v>
+        <v>103.8</v>
       </c>
       <c r="G4" t="n">
-        <v>31.9</v>
+        <v>34.6</v>
       </c>
       <c r="H4" t="n">
-        <v>20</v>
+        <v>19.7</v>
       </c>
       <c r="I4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J4" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="K4" t="n">
         <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="M4" t="n">
         <v>1</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>10.5</v>
+        <v>9.5</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>high-minutes, primary-scorer, efficient</t>
+          <t>high-minutes, primary-scorer, impact</t>
         </is>
       </c>
     </row>
@@ -955,70 +955,145 @@
         </is>
       </c>
       <c r="D5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" t="n">
         <v>2</v>
       </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
       <c r="F5" t="n">
-        <v>56.2</v>
+        <v>79.8</v>
       </c>
       <c r="G5" t="n">
-        <v>28.1</v>
+        <v>26.6</v>
       </c>
       <c r="H5" t="n">
-        <v>10.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J5" t="n">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="K5" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="L5" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>55.6%</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr"/>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>80.8%</t>
+          <t>60.5%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>80.8%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="S5" t="n">
+        <v>3</v>
+      </c>
+      <c r="T5" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>high-minutes, efficient, shooter</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Sampaense Inspecentro</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>M. Mboup</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" t="n">
         <v>2</v>
       </c>
-      <c r="T5" t="n">
-        <v>17</v>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>high-minutes, efficient, shooter</t>
+      <c r="F6" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="G6" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-21.6</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>rotation</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U5"/>
+  <autoFilter ref="A1:U6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1146,10 +1221,10 @@
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -1169,31 +1244,31 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>12.7</v>
+        <v>15.8</v>
       </c>
       <c r="G3" t="n">
-        <v>91.7</v>
+        <v>93.7</v>
       </c>
       <c r="H3" t="n">
-        <v>82.2</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>9.5</v>
+        <v>17.7</v>
       </c>
       <c r="J3" t="n">
         <v>2</v>
       </c>
       <c r="K3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L3" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
@@ -1213,31 +1288,31 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>12.7</v>
+        <v>15.8</v>
       </c>
       <c r="G4" t="n">
-        <v>91.7</v>
+        <v>93.7</v>
       </c>
       <c r="H4" t="n">
-        <v>82.2</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>9.5</v>
+        <v>17.7</v>
       </c>
       <c r="J4" t="n">
         <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L4" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -1341,22 +1416,22 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G2" t="n">
-        <v>66.8</v>
+        <v>98.7</v>
       </c>
       <c r="H2" t="n">
-        <v>84.40000000000001</v>
+        <v>79</v>
       </c>
       <c r="I2" t="n">
-        <v>85</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.6</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="3">
@@ -1377,26 +1452,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>M. Tavares | T. Espada</t>
+          <t>D. Hall | T. Espada</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G3" t="n">
-        <v>52</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>92.3</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>85.40000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>6.9</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="4">
@@ -1417,26 +1492,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>D. Hall | M. Tavares</t>
+          <t>D. Hall | T. Espada</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G4" t="n">
-        <v>59.3</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>87.59999999999999</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>84.2</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="5">
@@ -1461,22 +1536,22 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G5" t="n">
-        <v>53.5</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>88.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>86.7</v>
+        <v>82</v>
       </c>
       <c r="J5" t="n">
-        <v>1.5</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="6">
@@ -1501,22 +1576,22 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G6" t="n">
-        <v>42.5</v>
+        <v>65.3</v>
       </c>
       <c r="H6" t="n">
-        <v>96.8</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>81.8</v>
+        <v>73.5</v>
       </c>
       <c r="J6" t="n">
-        <v>15</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="7">
@@ -1541,22 +1616,22 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G7" t="n">
-        <v>42.5</v>
+        <v>65.3</v>
       </c>
       <c r="H7" t="n">
-        <v>96.8</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>81.8</v>
+        <v>73.5</v>
       </c>
       <c r="J7" t="n">
-        <v>15</v>
+        <v>15.9</v>
       </c>
     </row>
   </sheetData>
